--- a/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 11,61</t>
+          <t>7,84; 11,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 12,71</t>
+          <t>8,84; 12,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 19,52</t>
+          <t>14,13; 19,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 31,17</t>
+          <t>24,02; 31,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 16,86</t>
+          <t>13,05; 16,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,42</t>
+          <t>14,37; 18,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 22,92</t>
+          <t>17,82; 22,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,97; 38,14</t>
+          <t>32,62; 38,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,3; 14,03</t>
+          <t>11,27; 14,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,57</t>
+          <t>12,63; 15,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 20,77</t>
+          <t>16,9; 20,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 34,46</t>
+          <t>30,04; 34,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,66</t>
+          <t>4,47; 6,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,29</t>
+          <t>5,11; 7,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,07</t>
+          <t>8,47; 11,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 17,14</t>
+          <t>9,84; 17,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,05</t>
+          <t>3,06; 5,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,82</t>
+          <t>3,72; 5,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,12</t>
+          <t>8,43; 11,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,02</t>
+          <t>7,51; 12,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,49</t>
+          <t>4,06; 5,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,26</t>
+          <t>4,7; 6,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 10,59</t>
+          <t>8,84; 10,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,22</t>
+          <t>10,08; 14,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 11,25</t>
+          <t>6,25; 11,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,59</t>
+          <t>9,41; 15,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 21,42</t>
+          <t>14,4; 21,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,44</t>
+          <t>12,42; 17,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,27</t>
+          <t>5,72; 10,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 14,33</t>
+          <t>8,32; 14,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,08</t>
+          <t>10,19; 16,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,3</t>
+          <t>12,93; 17,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,05</t>
+          <t>6,69; 10,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,53; 13,78</t>
+          <t>9,54; 13,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 17,61</t>
+          <t>13,08; 17,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 16,9</t>
+          <t>13,38; 17,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,17</t>
+          <t>6,35; 8,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,33</t>
+          <t>7,27; 9,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 13,86</t>
+          <t>11,44; 13,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,03; 18,59</t>
+          <t>13,04; 18,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,81</t>
+          <t>7,82; 9,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 10,95</t>
+          <t>8,81; 10,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,46</t>
+          <t>12,02; 14,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,47; 17,96</t>
+          <t>13,39; 17,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,68</t>
+          <t>7,42; 8,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 9,84</t>
+          <t>8,39; 9,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,73</t>
+          <t>12,12; 13,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 17,91</t>
+          <t>14,34; 17,82</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81876; 119790</t>
+          <t>80843; 119793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85229; 123868</t>
+          <t>86169; 124883</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108263; 147228</t>
+          <t>106579; 148173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124391; 160490</t>
+          <t>123704; 161446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>170845; 221745</t>
+          <t>171622; 222974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>188811; 246376</t>
+          <t>192179; 247293</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>178453; 227972</t>
+          <t>177239; 228622</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249057; 288172</t>
+          <t>246479; 288730</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>265234; 329304</t>
+          <t>264376; 330038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>291270; 360100</t>
+          <t>291959; 361052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>294340; 363328</t>
+          <t>295496; 363218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>383655; 437805</t>
+          <t>381668; 435620</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72765; 112744</t>
+          <t>75692; 114554</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99631; 143233</t>
+          <t>100313; 147586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175498; 229931</t>
+          <t>175853; 233760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230016; 392626</t>
+          <t>225393; 395498</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46937; 80236</t>
+          <t>48553; 80328</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64450; 102334</t>
+          <t>65439; 101099</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165798; 221159</t>
+          <t>167559; 220862</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>173501; 268956</t>
+          <t>168076; 272118</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130583; 180047</t>
+          <t>133343; 183335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172446; 232819</t>
+          <t>174751; 233979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>356531; 430571</t>
+          <t>359376; 435993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>458422; 644072</t>
+          <t>456498; 644643</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33829; 62039</t>
+          <t>34453; 63527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45181; 75034</t>
+          <t>45257; 74783</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80652; 117126</t>
+          <t>78768; 117467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80391; 119229</t>
+          <t>80307; 115854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27230; 48934</t>
+          <t>27248; 49269</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38265; 65734</t>
+          <t>38162; 66347</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54984; 88328</t>
+          <t>55960; 89003</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85374; 114248</t>
+          <t>85422; 117042</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68560; 103290</t>
+          <t>68732; 102863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89534; 129486</t>
+          <t>89669; 130729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141131; 193003</t>
+          <t>143371; 194890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>172237; 220858</t>
+          <t>174947; 224523</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>209536; 267820</t>
+          <t>208080; 268121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>246690; 319112</t>
+          <t>248647; 317183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>389902; 468247</t>
+          <t>386298; 463286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>449658; 641760</t>
+          <t>450238; 639860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>263461; 331569</t>
+          <t>264324; 329422</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>312352; 389335</t>
+          <t>313274; 387021</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>426949; 510664</t>
+          <t>424503; 507225</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>492241; 656244</t>
+          <t>489164; 654299</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>489298; 577801</t>
+          <t>494099; 579992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>585563; 686457</t>
+          <t>584901; 683835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>833335; 948919</t>
+          <t>837130; 948290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1028205; 1272746</t>
+          <t>1019083; 1266190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,61</t>
+          <t>7,82; 11,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,81</t>
+          <t>8,78; 13,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 19,64</t>
+          <t>14,15; 19,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 31,35</t>
+          <t>24,48; 31,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,95</t>
+          <t>13,01; 16,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,49</t>
+          <t>14,42; 18,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 22,98</t>
+          <t>17,63; 23,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,62; 38,22</t>
+          <t>32,37; 37,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 14,06</t>
+          <t>11,25; 14,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 15,61</t>
+          <t>12,46; 15,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,9; 20,77</t>
+          <t>17,01; 20,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 34,29</t>
+          <t>30,08; 34,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,76</t>
+          <t>4,41; 6,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,51</t>
+          <t>5,12; 7,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,26</t>
+          <t>8,3; 10,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,27</t>
+          <t>15,24; 18,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,06</t>
+          <t>3,08; 5,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,75</t>
+          <t>3,63; 5,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,11</t>
+          <t>8,58; 11,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 12,16</t>
+          <t>10,83; 13,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,59</t>
+          <t>4,02; 5,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 6,29</t>
+          <t>4,69; 6,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 10,73</t>
+          <t>8,74; 10,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,24</t>
+          <t>13,38; 15,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,52</t>
+          <t>6,5; 11,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 15,54</t>
+          <t>9,07; 15,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 21,48</t>
+          <t>14,46; 21,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,92</t>
+          <t>12,86; 18,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,34</t>
+          <t>5,5; 10,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 14,47</t>
+          <t>8,14; 14,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,21</t>
+          <t>10,12; 16,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,72</t>
+          <t>12,66; 17,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,01</t>
+          <t>6,61; 9,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 13,91</t>
+          <t>9,52; 14,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 17,78</t>
+          <t>13,16; 17,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 17,18</t>
+          <t>13,44; 17,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,18</t>
+          <t>6,39; 8,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,27</t>
+          <t>7,35; 9,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,72</t>
+          <t>11,5; 13,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 18,54</t>
+          <t>17,12; 19,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,75</t>
+          <t>7,74; 9,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,89</t>
+          <t>8,85; 10,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 14,36</t>
+          <t>11,99; 14,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,39; 17,91</t>
+          <t>16,57; 18,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,71</t>
+          <t>7,36; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 9,81</t>
+          <t>8,34; 9,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 13,72</t>
+          <t>12,06; 13,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,82</t>
+          <t>17,05; 18,83</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>163184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>267797</t>
+          <t>286308</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>408861</t>
+          <t>449492</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80843; 119793</t>
+          <t>80649; 120038</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86169; 124883</t>
+          <t>85603; 127375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106579; 148173</t>
+          <t>106738; 145693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123704; 161446</t>
+          <t>141604; 185030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>171622; 222974</t>
+          <t>171139; 222696</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>192179; 247293</t>
+          <t>192973; 247506</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>177239; 228622</t>
+          <t>175362; 230398</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>246479; 288730</t>
+          <t>266116; 308352</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>264376; 330038</t>
+          <t>263996; 331567</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>291959; 361052</t>
+          <t>288235; 360174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295496; 363218</t>
+          <t>297583; 366084</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>381668; 435620</t>
+          <t>421330; 480367</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>338199</t>
+          <t>374581</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>232189</t>
+          <t>258961</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>570388</t>
+          <t>633542</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75692; 114554</t>
+          <t>74744; 114346</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100313; 147586</t>
+          <t>100532; 146323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175853; 233760</t>
+          <t>172379; 226837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225393; 395498</t>
+          <t>339942; 414758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48553; 80328</t>
+          <t>48872; 82709</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65439; 101099</t>
+          <t>63821; 103078</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>167559; 220862</t>
+          <t>170559; 225777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168076; 272118</t>
+          <t>235207; 286282</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133343; 183335</t>
+          <t>131952; 181504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174751; 233979</t>
+          <t>174430; 233308</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>359376; 435993</t>
+          <t>355061; 431008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>456498; 644643</t>
+          <t>589179; 679231</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96699</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99838</t>
+          <t>109443</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>196537</t>
+          <t>218987</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34453; 63527</t>
+          <t>35862; 62913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45257; 74783</t>
+          <t>43666; 76849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78768; 117467</t>
+          <t>79064; 117386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80307; 115854</t>
+          <t>91507; 130136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27248; 49269</t>
+          <t>26200; 49223</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38162; 66347</t>
+          <t>37319; 65740</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55960; 89003</t>
+          <t>55599; 88424</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85422; 117042</t>
+          <t>93054; 127174</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68732; 102863</t>
+          <t>67900; 102201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89669; 130729</t>
+          <t>89512; 132528</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143371; 194890</t>
+          <t>144291; 193022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>174947; 224523</t>
+          <t>194395; 247257</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575962</t>
+          <t>647310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>599825</t>
+          <t>654711</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1175786</t>
+          <t>1302021</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>208080; 268121</t>
+          <t>209412; 271884</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>248647; 317183</t>
+          <t>251230; 319401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>386298; 463286</t>
+          <t>388326; 468811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450238; 639860</t>
+          <t>602917; 698325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>264324; 329422</t>
+          <t>261588; 329584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>313274; 387021</t>
+          <t>314678; 388887</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>424503; 507225</t>
+          <t>423660; 506910</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>489164; 654299</t>
+          <t>617679; 694076</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>494099; 579992</t>
+          <t>489979; 582606</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>584901; 683835</t>
+          <t>581328; 687337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>837130; 948290</t>
+          <t>833542; 946142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1019083; 1266190</t>
+          <t>1235685; 1364671</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
